--- a/backend/excel-templates/test-data/master_upload_test_data.xlsx
+++ b/backend/excel-templates/test-data/master_upload_test_data.xlsx
@@ -398,6 +398,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I51"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="50.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,1460 +433,1460 @@
         <v>Supervisor</v>
       </c>
       <c r="H1" t="str">
-        <v>External_mid_term</v>
+        <v>External Mid Term</v>
       </c>
       <c r="I1" t="str">
-        <v>External_final</v>
+        <v>External Final</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ram Dahal</v>
+        <v>Shyam Gurung 1</v>
       </c>
       <c r="B2" t="str">
-        <v>080MSNCS01</v>
+        <v>79MSICE02</v>
       </c>
       <c r="C2" t="str">
-        <v>Machine Learning for Early Detection of Crop Diseases</v>
+        <v>Blockchain-Based Land Registry System for Nepal (Student 1)</v>
       </c>
       <c r="D2" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E2" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F2" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G2" t="str">
-        <v>Prof. Dr. Rajan Sharma</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="H2" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I2" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Shyam Gurung</v>
+        <v>Sita Adhikari 2</v>
       </c>
       <c r="B3" t="str">
-        <v>080MSICE02</v>
+        <v>79MSDSA03</v>
       </c>
       <c r="C3" t="str">
-        <v>Blockchain-Based Land Registry System for Nepal</v>
+        <v>IoT-Enabled Smart Grid for Rural Electrification (Student 2)</v>
       </c>
       <c r="D3" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E3" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F3" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G3" t="str">
-        <v>Dr. Pramod Acharya</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="H3" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I3" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Hari Khadka</v>
+        <v>Gita Bhandari 3</v>
       </c>
       <c r="B4" t="str">
-        <v>080MSDSA03</v>
+        <v>79MSCSKE04</v>
       </c>
       <c r="C4" t="str">
-        <v>Natural Language Processing for Nepali Text Summarization</v>
+        <v>Deep Learning for Medical Image Diagnosis (Student 3)</v>
       </c>
       <c r="D4" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E4" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F4" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G4" t="str">
-        <v>Assoc. Prof. Sita Dahal</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="H4" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I4" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sita Lama</v>
+        <v>Hari Thapa 4</v>
       </c>
       <c r="B5" t="str">
-        <v>080MSCSKE04</v>
+        <v>79MSNCS05</v>
       </c>
       <c r="C5" t="str">
-        <v>IoT-Enabled Smart Grid for Rural Electrification</v>
+        <v>Cloud-Based E-Governance Framework (Student 4)</v>
       </c>
       <c r="D5" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E5" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F5" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G5" t="str">
-        <v>Dr. Bishnu Poudel</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="H5" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I5" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Gita Maharjan</v>
+        <v>Krishna Poudel 5</v>
       </c>
       <c r="B6" t="str">
-        <v>080MSNCS05</v>
+        <v>79MSICE06</v>
       </c>
       <c r="C6" t="str">
-        <v>Deep Learning Approach for Medical Image Diagnosis</v>
+        <v>Natural Language Processing for Nepali Text (Student 5)</v>
       </c>
       <c r="D6" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E6" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F6" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G6" t="str">
-        <v>Prof. Gita Thapa</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="H6" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I6" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Rita Neupane</v>
+        <v>Arjun Sharma 6</v>
       </c>
       <c r="B7" t="str">
-        <v>080MSICE06</v>
+        <v>79MSDSA07</v>
       </c>
       <c r="C7" t="str">
-        <v>Cloud Computing Framework for E-Government Services</v>
+        <v>Cybersecurity Framework for Financial Institutions (Student 6)</v>
       </c>
       <c r="D7" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E7" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F7" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G7" t="str">
-        <v>Dr. Mohan Basnet</v>
+        <v>Prof. Dr. Rajan Sharma</v>
       </c>
       <c r="H7" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I7" t="str">
-        <v>Assoc. Prof. Sarita Ghimire</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Krishna Ojha</v>
+        <v>Bishnu Neupane 7</v>
       </c>
       <c r="B8" t="str">
-        <v>080MSDSA07</v>
+        <v>79MSCSKE08</v>
       </c>
       <c r="C8" t="str">
-        <v>Computer Vision for Traffic Violation Detection</v>
+        <v>AI-Powered Recommendation System for E-Commerce (Student 7)</v>
       </c>
       <c r="D8" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E8" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F8" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G8" t="str">
-        <v>Assoc. Prof. Reema Rai</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="H8" t="str">
-        <v>Assoc. Prof. Sarita Ghimire</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I8" t="str">
-        <v>Dr. Pratik Thapa</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bishnu Pandey</v>
+        <v>Ram Dahal 8</v>
       </c>
       <c r="B9" t="str">
-        <v>080MSCSKE08</v>
+        <v>79MSNCS09</v>
       </c>
       <c r="C9" t="str">
-        <v>Reinforcement Learning for Autonomous Vehicle Navigation</v>
+        <v>Edge Computing for Real-Time Data Processing (Student 8)</v>
       </c>
       <c r="D9" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E9" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F9" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G9" t="str">
-        <v>Dr. Deepak Neupane</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="H9" t="str">
-        <v>Dr. Pratik Thapa</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I9" t="str">
-        <v>Prof. Anjana Shrestha</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Arjun Rai</v>
+        <v>Shyam Gurung 9</v>
       </c>
       <c r="B10" t="str">
-        <v>080MSNCS09</v>
+        <v>79MSICE10</v>
       </c>
       <c r="C10" t="str">
-        <v>Big Data Analytics for Tourism Pattern Prediction</v>
+        <v>Federated Learning for Privacy-Preserving Data Analytics (Student 9)</v>
       </c>
       <c r="D10" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E10" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F10" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G10" t="str">
-        <v>Prof. Kabita Khadka</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="H10" t="str">
-        <v>Prof. Anjana Shrestha</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I10" t="str">
-        <v>Dr. Bibek Pradhan</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Pratik Sharma</v>
+        <v>Sita Adhikari 10</v>
       </c>
       <c r="B11" t="str">
-        <v>080MSICE10</v>
+        <v>79MSDSA11</v>
       </c>
       <c r="C11" t="str">
-        <v>Cybersecurity Framework for Financial Transactions</v>
+        <v>Computer Vision for Autonomous Vehicle Navigation (Student 10)</v>
       </c>
       <c r="D11" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E11" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F11" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G11" t="str">
-        <v>Dr. Nabin Pandey</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="H11" t="str">
-        <v>Dr. Bibek Pradhan</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I11" t="str">
-        <v>Assoc. Prof. Tara Rana</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Nabin Thapa</v>
+        <v>Gita Bhandari 11</v>
       </c>
       <c r="B12" t="str">
-        <v>080MSDSA11</v>
+        <v>79MSCSKE12</v>
       </c>
       <c r="C12" t="str">
-        <v>Sentiment Analysis of Nepali Social Media Content</v>
+        <v>5G Network Slicing for IoT Applications (Student 11)</v>
       </c>
       <c r="D12" t="str">
-        <v>080</v>
+        <v>79</v>
       </c>
       <c r="E12" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F12" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G12" t="str">
-        <v>Assoc. Prof. Mina Gurung</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="H12" t="str">
-        <v>Assoc. Prof. Tara Rana</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I12" t="str">
-        <v>Dr. Krishna Subedi</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Sagar Poudel</v>
+        <v>Hari Thapa 12</v>
       </c>
       <c r="B13" t="str">
-        <v>080MSCSKE12</v>
+        <v>80MSNCS13</v>
       </c>
       <c r="C13" t="str">
-        <v>Edge Computing Architecture for Real-Time Monitoring</v>
+        <v>Quantum Machine Learning Algorithms (Student 12)</v>
       </c>
       <c r="D13" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E13" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F13" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G13" t="str">
-        <v>Dr. Prakash Chhetri</v>
+        <v>Prof. Dr. Rajan Sharma</v>
       </c>
       <c r="H13" t="str">
-        <v>Dr. Krishna Subedi</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I13" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Roshan Pokhrel</v>
+        <v>Krishna Poudel 13</v>
       </c>
       <c r="B14" t="str">
-        <v>080MSNCS13</v>
+        <v>80MSICE14</v>
       </c>
       <c r="C14" t="str">
-        <v>Federated Learning for Privacy-Preserving Healthcare</v>
+        <v>Big Data Analytics for Smart City Planning (Student 13)</v>
       </c>
       <c r="D14" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E14" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F14" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G14" t="str">
-        <v>Prof. Dr. Rajan Sharma</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="H14" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I14" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Bibek Adhikari</v>
+        <v>Arjun Sharma 14</v>
       </c>
       <c r="B15" t="str">
-        <v>080MSICE14</v>
+        <v>80MSDSA15</v>
       </c>
       <c r="C15" t="str">
-        <v>Optical Character Recognition for Nepali Scripts</v>
+        <v>Reinforcement Learning for Robotics Control (Student 14)</v>
       </c>
       <c r="D15" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E15" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F15" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G15" t="str">
-        <v>Dr. Pramod Acharya</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="H15" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I15" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Amit Bhandari</v>
+        <v>Bishnu Neupane 15</v>
       </c>
       <c r="B16" t="str">
-        <v>080MSDSA15</v>
+        <v>80MSCSKE16</v>
       </c>
       <c r="C16" t="str">
-        <v>Wireless Sensor Network for Earthquake Early Warning</v>
+        <v>Machine Learning for Early Detection of Crop Diseases (Student 15)</v>
       </c>
       <c r="D16" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E16" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F16" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G16" t="str">
-        <v>Assoc. Prof. Sita Dahal</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="H16" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I16" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Sunita Acharya</v>
+        <v>Ram Dahal 16</v>
       </c>
       <c r="B17" t="str">
-        <v>080MSCSKE16</v>
+        <v>80MSNCS17</v>
       </c>
       <c r="C17" t="str">
-        <v>AI-Powered Chatbot for Student Advisory Services</v>
+        <v>Blockchain-Based Land Registry System for Nepal (Student 16)</v>
       </c>
       <c r="D17" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E17" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F17" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G17" t="str">
-        <v>Dr. Bishnu Poudel</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="H17" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I17" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Kabita Basnet</v>
+        <v>Shyam Gurung 17</v>
       </c>
       <c r="B18" t="str">
-        <v>080MSNCS17</v>
+        <v>80MSICE18</v>
       </c>
       <c r="C18" t="str">
-        <v>Robotic Process Automation in Healthcare Administration</v>
+        <v>IoT-Enabled Smart Grid for Rural Electrification (Student 17)</v>
       </c>
       <c r="D18" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E18" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F18" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G18" t="str">
-        <v>Prof. Gita Thapa</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="H18" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I18" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Pooja Chhetri</v>
+        <v>Sita Adhikari 18</v>
       </c>
       <c r="B19" t="str">
-        <v>080MSICE18</v>
+        <v>80MSDSA19</v>
       </c>
       <c r="C19" t="str">
-        <v>Augmented Reality for Cultural Heritage Preservation</v>
+        <v>Deep Learning for Medical Image Diagnosis (Student 18)</v>
       </c>
       <c r="D19" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E19" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F19" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G19" t="str">
-        <v>Dr. Mohan Basnet</v>
+        <v>Prof. Dr. Rajan Sharma</v>
       </c>
       <c r="H19" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I19" t="str">
-        <v>Assoc. Prof. Sarita Ghimire</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Anita Dahal</v>
+        <v>Gita Bhandari 19</v>
       </c>
       <c r="B20" t="str">
-        <v>080MSDSA19</v>
+        <v>80MSCSKE20</v>
       </c>
       <c r="C20" t="str">
-        <v>Quantum Cryptography for Secure Communications</v>
+        <v>Cloud-Based E-Governance Framework (Student 19)</v>
       </c>
       <c r="D20" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E20" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F20" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G20" t="str">
-        <v>Assoc. Prof. Reema Rai</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="H20" t="str">
-        <v>Assoc. Prof. Sarita Ghimire</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I20" t="str">
-        <v>Dr. Pratik Thapa</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Sarita Gurung</v>
+        <v>Hari Thapa 20</v>
       </c>
       <c r="B21" t="str">
-        <v>080MSCSKE20</v>
+        <v>80MSNCS21</v>
       </c>
       <c r="C21" t="str">
-        <v>Speech Recognition System for Nepali Language</v>
+        <v>Natural Language Processing for Nepali Text (Student 20)</v>
       </c>
       <c r="D21" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E21" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F21" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G21" t="str">
-        <v>Dr. Deepak Neupane</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="H21" t="str">
-        <v>Dr. Pratik Thapa</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I21" t="str">
-        <v>Prof. Anjana Shrestha</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Deepak Khadka</v>
+        <v>Krishna Poudel 21</v>
       </c>
       <c r="B22" t="str">
-        <v>080MSNCS21</v>
+        <v>80MSICE22</v>
       </c>
       <c r="C22" t="str">
-        <v>Smart Waste Management Using IoT Sensors</v>
+        <v>Cybersecurity Framework for Financial Institutions (Student 21)</v>
       </c>
       <c r="D22" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E22" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F22" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G22" t="str">
-        <v>Prof. Kabita Khadka</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="H22" t="str">
-        <v>Prof. Anjana Shrestha</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I22" t="str">
-        <v>Dr. Bibek Pradhan</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Mohan Lama</v>
+        <v>Arjun Sharma 22</v>
       </c>
       <c r="B23" t="str">
-        <v>080MSICE22</v>
+        <v>80MSDSA23</v>
       </c>
       <c r="C23" t="str">
-        <v>Predictive Maintenance Using Machine Learning</v>
+        <v>AI-Powered Recommendation System for E-Commerce (Student 22)</v>
       </c>
       <c r="D23" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E23" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F23" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G23" t="str">
-        <v>Dr. Nabin Pandey</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="H23" t="str">
-        <v>Dr. Bibek Pradhan</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I23" t="str">
-        <v>Assoc. Prof. Tara Rana</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Rajan Maharjan</v>
+        <v>Bishnu Neupane 23</v>
       </c>
       <c r="B24" t="str">
-        <v>080MSDSA23</v>
+        <v>80MSCSKE24</v>
       </c>
       <c r="C24" t="str">
-        <v>Recommendation System for E-Learning Platforms</v>
+        <v>Edge Computing for Real-Time Data Processing (Student 23)</v>
       </c>
       <c r="D24" t="str">
-        <v>080</v>
+        <v>80</v>
       </c>
       <c r="E24" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F24" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G24" t="str">
-        <v>Assoc. Prof. Mina Gurung</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="H24" t="str">
-        <v>Assoc. Prof. Tara Rana</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I24" t="str">
-        <v>Dr. Krishna Subedi</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Umesh Neupane</v>
+        <v>Ram Dahal 24</v>
       </c>
       <c r="B25" t="str">
-        <v>080MSCSKE24</v>
+        <v>81MSNCS01</v>
       </c>
       <c r="C25" t="str">
-        <v>Image Segmentation for Agricultural Land Classification</v>
+        <v>Federated Learning for Privacy-Preserving Data Analytics (Student 24)</v>
       </c>
       <c r="D25" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E25" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F25" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G25" t="str">
-        <v>Dr. Prakash Chhetri</v>
+        <v>Prof. Dr. Rajan Sharma</v>
       </c>
       <c r="H25" t="str">
-        <v>Dr. Krishna Subedi</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I25" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Prakash Ojha</v>
+        <v>Shyam Gurung 25</v>
       </c>
       <c r="B26" t="str">
-        <v>080MSNCS25</v>
+        <v>81MSICE02</v>
       </c>
       <c r="C26" t="str">
-        <v>Time Series Forecasting for Hydropower Generation</v>
+        <v>Computer Vision for Autonomous Vehicle Navigation (Student 25)</v>
       </c>
       <c r="D26" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E26" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F26" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G26" t="str">
-        <v>Prof. Dr. Rajan Sharma</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="H26" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I26" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Mina Pandey</v>
+        <v>Sita Adhikari 26</v>
       </c>
       <c r="B27" t="str">
-        <v>080MSICE26</v>
+        <v>81MSDSA03</v>
       </c>
       <c r="C27" t="str">
-        <v>Mobile Health Application for Remote Patient Monitoring</v>
+        <v>5G Network Slicing for IoT Applications (Student 26)</v>
       </c>
       <c r="D27" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E27" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F27" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G27" t="str">
-        <v>Dr. Pramod Acharya</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="H27" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I27" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Tara Rai</v>
+        <v>Gita Bhandari 27</v>
       </c>
       <c r="B28" t="str">
-        <v>080MSDSA27</v>
+        <v>81MSCSKE04</v>
       </c>
       <c r="C28" t="str">
-        <v>Sustainable Energy Optimization Using AI</v>
+        <v>Quantum Machine Learning Algorithms (Student 27)</v>
       </c>
       <c r="D28" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E28" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F28" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G28" t="str">
-        <v>Assoc. Prof. Sita Dahal</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="H28" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I28" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Reema Sharma</v>
+        <v>Hari Thapa 28</v>
       </c>
       <c r="B29" t="str">
-        <v>080MSCSKE28</v>
+        <v>81MSNCS05</v>
       </c>
       <c r="C29" t="str">
-        <v>Automated Essay Scoring in Nepali Education</v>
+        <v>Big Data Analytics for Smart City Planning (Student 28)</v>
       </c>
       <c r="D29" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E29" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F29" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G29" t="str">
-        <v>Dr. Bishnu Poudel</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="H29" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I29" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Sushma Thapa</v>
+        <v>Krishna Poudel 29</v>
       </c>
       <c r="B30" t="str">
-        <v>080MSNCS29</v>
+        <v>81MSICE06</v>
       </c>
       <c r="C30" t="str">
-        <v>Face Recognition System for Attendance Management</v>
+        <v>Reinforcement Learning for Robotics Control (Student 29)</v>
       </c>
       <c r="D30" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E30" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F30" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G30" t="str">
-        <v>Prof. Gita Thapa</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="H30" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I30" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Anjana Poudel</v>
+        <v>Arjun Sharma 30</v>
       </c>
       <c r="B31" t="str">
-        <v>080MSICE30</v>
+        <v>81MSDSA07</v>
       </c>
       <c r="C31" t="str">
-        <v>Gesture Recognition for Human-Computer Interaction</v>
+        <v>Machine Learning for Early Detection of Crop Diseases (Student 30)</v>
       </c>
       <c r="D31" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E31" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F31" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G31" t="str">
-        <v>Dr. Mohan Basnet</v>
+        <v>Prof. Dr. Rajan Sharma</v>
       </c>
       <c r="H31" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I31" t="str">
-        <v>Assoc. Prof. Sarita Ghimire</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ram Pokhrel</v>
+        <v>Bishnu Neupane 31</v>
       </c>
       <c r="B32" t="str">
-        <v>080MSDSA31</v>
+        <v>81MSCSKE08</v>
       </c>
       <c r="C32" t="str">
-        <v>Anomaly Detection in Network Traffic Using Deep Learning</v>
+        <v>Blockchain-Based Land Registry System for Nepal (Student 31)</v>
       </c>
       <c r="D32" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E32" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F32" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G32" t="str">
-        <v>Assoc. Prof. Reema Rai</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="H32" t="str">
-        <v>Assoc. Prof. Sarita Ghimire</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I32" t="str">
-        <v>Dr. Pratik Thapa</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Shyam Adhikari</v>
+        <v>Ram Dahal 32</v>
       </c>
       <c r="B33" t="str">
-        <v>080MSCSKE32</v>
+        <v>81MSNCS09</v>
       </c>
       <c r="C33" t="str">
-        <v>Blockchain for Supply Chain Transparency</v>
+        <v>IoT-Enabled Smart Grid for Rural Electrification (Student 32)</v>
       </c>
       <c r="D33" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E33" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F33" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G33" t="str">
-        <v>Dr. Deepak Neupane</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="H33" t="str">
-        <v>Dr. Pratik Thapa</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I33" t="str">
-        <v>Prof. Anjana Shrestha</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Hari Bhandari</v>
+        <v>Shyam Gurung 33</v>
       </c>
       <c r="B34" t="str">
-        <v>080MSNCS33</v>
+        <v>81MSICE10</v>
       </c>
       <c r="C34" t="str">
-        <v>Emotion Recognition from Speech Signals</v>
+        <v>Deep Learning for Medical Image Diagnosis (Student 33)</v>
       </c>
       <c r="D34" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E34" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F34" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G34" t="str">
-        <v>Prof. Kabita Khadka</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="H34" t="str">
-        <v>Prof. Anjana Shrestha</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I34" t="str">
-        <v>Dr. Bibek Pradhan</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sita Acharya</v>
+        <v>Sita Adhikari 34</v>
       </c>
       <c r="B35" t="str">
-        <v>080MSICE34</v>
+        <v>81MSDSA11</v>
       </c>
       <c r="C35" t="str">
-        <v>Document Classification in Legal Domain</v>
+        <v>Cloud-Based E-Governance Framework (Student 34)</v>
       </c>
       <c r="D35" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E35" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F35" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G35" t="str">
-        <v>Dr. Nabin Pandey</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="H35" t="str">
-        <v>Dr. Bibek Pradhan</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I35" t="str">
-        <v>Assoc. Prof. Tara Rana</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gita Basnet</v>
+        <v>Gita Bhandari 35</v>
       </c>
       <c r="B36" t="str">
-        <v>080MSDSA35</v>
+        <v>81MSCSKE12</v>
       </c>
       <c r="C36" t="str">
-        <v>Video Analytics for Crowd Management</v>
+        <v>Natural Language Processing for Nepali Text (Student 35)</v>
       </c>
       <c r="D36" t="str">
-        <v>080</v>
+        <v>81</v>
       </c>
       <c r="E36" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F36" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G36" t="str">
-        <v>Assoc. Prof. Mina Gurung</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="H36" t="str">
-        <v>Assoc. Prof. Tara Rana</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I36" t="str">
-        <v>Dr. Krishna Subedi</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Rita Chhetri</v>
+        <v>Hari Thapa 36</v>
       </c>
       <c r="B37" t="str">
-        <v>080MSCSKE36</v>
+        <v>82MSNCS13</v>
       </c>
       <c r="C37" t="str">
-        <v>Multi-Agent System for Disaster Response</v>
+        <v>Cybersecurity Framework for Financial Institutions (Student 36)</v>
       </c>
       <c r="D37" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E37" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F37" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G37" t="str">
-        <v>Dr. Prakash Chhetri</v>
+        <v>Prof. Dr. Rajan Sharma</v>
       </c>
       <c r="H37" t="str">
-        <v>Dr. Krishna Subedi</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I37" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Krishna Dahal</v>
+        <v>Krishna Poudel 37</v>
       </c>
       <c r="B38" t="str">
-        <v>080MSNCS37</v>
+        <v>82MSICE14</v>
       </c>
       <c r="C38" t="str">
-        <v>Knowledge Graph for Research Publication Analysis</v>
+        <v>AI-Powered Recommendation System for E-Commerce (Student 37)</v>
       </c>
       <c r="D38" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E38" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F38" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G38" t="str">
-        <v>Prof. Dr. Rajan Sharma</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="H38" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I38" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bishnu Gurung</v>
+        <v>Arjun Sharma 38</v>
       </c>
       <c r="B39" t="str">
-        <v>080MSICE38</v>
+        <v>82MSDSA15</v>
       </c>
       <c r="C39" t="str">
-        <v>Transfer Learning for Low-Resource Nepali NLP</v>
+        <v>Edge Computing for Real-Time Data Processing (Student 38)</v>
       </c>
       <c r="D39" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E39" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F39" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G39" t="str">
-        <v>Dr. Pramod Acharya</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="H39" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I39" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Arjun Khadka</v>
+        <v>Bishnu Neupane 39</v>
       </c>
       <c r="B40" t="str">
-        <v>080MSDSA39</v>
+        <v>82MSCSKE16</v>
       </c>
       <c r="C40" t="str">
-        <v>Explainable AI for Credit Risk Assessment</v>
+        <v>Federated Learning for Privacy-Preserving Data Analytics (Student 39)</v>
       </c>
       <c r="D40" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E40" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F40" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G40" t="str">
-        <v>Assoc. Prof. Sita Dahal</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="H40" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I40" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Pratik Lama</v>
+        <v>Ram Dahal 40</v>
       </c>
       <c r="B41" t="str">
-        <v>080MSCSKE40</v>
+        <v>82MSNCS17</v>
       </c>
       <c r="C41" t="str">
-        <v>Indoor Localization Using WiFi Fingerprinting</v>
+        <v>Computer Vision for Autonomous Vehicle Navigation (Student 40)</v>
       </c>
       <c r="D41" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E41" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F41" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G41" t="str">
-        <v>Dr. Bishnu Poudel</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="H41" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I41" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nabin Maharjan</v>
+        <v>Shyam Gurung 41</v>
       </c>
       <c r="B42" t="str">
-        <v>080MSNCS41</v>
+        <v>82MSICE18</v>
       </c>
       <c r="C42" t="str">
-        <v>Real-Time Sign Language Translation</v>
+        <v>5G Network Slicing for IoT Applications (Student 41)</v>
       </c>
       <c r="D42" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E42" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F42" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="H42" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I42" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Sagar Neupane</v>
+        <v>Sita Adhikari 42</v>
       </c>
       <c r="B43" t="str">
-        <v>080MSICE42</v>
+        <v>82MSDSA19</v>
       </c>
       <c r="C43" t="str">
-        <v>Data Privacy Framework for Social Media Platforms</v>
+        <v>Quantum Machine Learning Algorithms (Student 42)</v>
       </c>
       <c r="D43" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E43" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F43" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>Prof. Dr. Rajan Sharma</v>
       </c>
       <c r="H43" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I43" t="str">
-        <v>Assoc. Prof. Sarita Ghimire</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Roshan Ojha</v>
+        <v>Gita Bhandari 43</v>
       </c>
       <c r="B44" t="str">
-        <v>080MSDSA43</v>
+        <v>82MSCSKE20</v>
       </c>
       <c r="C44" t="str">
-        <v>Smart Irrigation System Using AI and IoT</v>
+        <v>Big Data Analytics for Smart City Planning (Student 43)</v>
       </c>
       <c r="D44" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E44" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F44" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="H44" t="str">
-        <v>Assoc. Prof. Sarita Ghimire</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I44" t="str">
-        <v>Dr. Pratik Thapa</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Bibek Pandey</v>
+        <v>Hari Thapa 44</v>
       </c>
       <c r="B45" t="str">
-        <v>080MSCSKE44</v>
+        <v>82MSNCS21</v>
       </c>
       <c r="C45" t="str">
-        <v>Cryptographic Protocol for Secure E-Voting</v>
+        <v>Reinforcement Learning for Robotics Control (Student 44)</v>
       </c>
       <c r="D45" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E45" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F45" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="H45" t="str">
-        <v>Dr. Pratik Thapa</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I45" t="str">
-        <v>Prof. Anjana Shrestha</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Amit Rai</v>
+        <v>Krishna Poudel 45</v>
       </c>
       <c r="B46" t="str">
-        <v>080MSNCS45</v>
+        <v>82MSICE22</v>
       </c>
       <c r="C46" t="str">
-        <v>Adaptive Learning System for Personalized Education</v>
+        <v>Machine Learning for Early Detection of Crop Diseases (Student 45)</v>
       </c>
       <c r="D46" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E46" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F46" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="H46" t="str">
-        <v>Prof. Anjana Shrestha</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I46" t="str">
-        <v>Dr. Bibek Pradhan</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Sunita Sharma</v>
+        <v>Arjun Sharma 46</v>
       </c>
       <c r="B47" t="str">
-        <v>080MSICE46</v>
+        <v>82MSDSA23</v>
       </c>
       <c r="C47" t="str">
-        <v>Digital Twin for Smart Manufacturing</v>
+        <v>Blockchain-Based Land Registry System for Nepal (Student 46)</v>
       </c>
       <c r="D47" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E47" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F47" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="H47" t="str">
-        <v>Dr. Bibek Pradhan</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I47" t="str">
-        <v>Assoc. Prof. Tara Rana</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Kabita Thapa</v>
+        <v>Bishnu Neupane 47</v>
       </c>
       <c r="B48" t="str">
-        <v>080MSDSA47</v>
+        <v>82MSCSKE24</v>
       </c>
       <c r="C48" t="str">
-        <v>Social Network Analysis for Misinformation Detection</v>
+        <v>IoT-Enabled Smart Grid for Rural Electrification (Student 47)</v>
       </c>
       <c r="D48" t="str">
-        <v>080</v>
+        <v>82</v>
       </c>
       <c r="E48" t="str">
-        <v>Cluster 3</v>
+        <v>Cluster 4</v>
       </c>
       <c r="F48" t="str">
-        <v>MSc in Data Science and Analytics</v>
+        <v>MSc in Computer Science and Knowledge Engineering</v>
       </c>
       <c r="G48" t="str">
-        <v/>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="H48" t="str">
-        <v>Assoc. Prof. Tara Rana</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
       <c r="I48" t="str">
-        <v>Dr. Krishna Subedi</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Pooja Poudel</v>
+        <v>Ram Dahal 48</v>
       </c>
       <c r="B49" t="str">
-        <v>080MSCSKE48</v>
+        <v>83MSNCS01</v>
       </c>
       <c r="C49" t="str">
-        <v>Autonomous Drone Navigation Using Computer Vision</v>
+        <v>Deep Learning for Medical Image Diagnosis (Student 48)</v>
       </c>
       <c r="D49" t="str">
-        <v>080</v>
+        <v>83</v>
       </c>
       <c r="E49" t="str">
-        <v>Cluster 4</v>
+        <v>Cluster 1</v>
       </c>
       <c r="F49" t="str">
-        <v>MSc in Computer Science and Knowledge Engineering</v>
+        <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>Prof. Dr. Rajan Sharma</v>
       </c>
       <c r="H49" t="str">
-        <v>Dr. Krishna Subedi</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I49" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Anita Pokhrel</v>
+        <v>Shyam Gurung 49</v>
       </c>
       <c r="B50" t="str">
-        <v>080MSNCS49</v>
+        <v>83MSICE02</v>
       </c>
       <c r="C50" t="str">
-        <v>Semantic Web Framework for Heritage Documentation</v>
+        <v>Cloud-Based E-Governance Framework (Student 49)</v>
       </c>
       <c r="D50" t="str">
-        <v>080</v>
+        <v>83</v>
       </c>
       <c r="E50" t="str">
-        <v>Cluster 1</v>
+        <v>Cluster 2</v>
       </c>
       <c r="F50" t="str">
-        <v>MSc in Network and Cyber Security</v>
+        <v>MSc in Information and Communication Engineering</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="H50" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
       <c r="I50" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Sarita Adhikari</v>
+        <v>Sita Adhikari 50</v>
       </c>
       <c r="B51" t="str">
-        <v>080MSICE50</v>
+        <v>83MSDSA03</v>
       </c>
       <c r="C51" t="str">
-        <v>End-to-End Encryption for Messaging Platforms</v>
+        <v>Natural Language Processing for Nepali Text (Student 50)</v>
       </c>
       <c r="D51" t="str">
-        <v>080</v>
+        <v>83</v>
       </c>
       <c r="E51" t="str">
-        <v>Cluster 2</v>
+        <v>Cluster 3</v>
       </c>
       <c r="F51" t="str">
-        <v>MSc in Information and Communication Engineering</v>
+        <v>MSc in Data Science and Analytics</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="H51" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
       <c r="I51" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
   </sheetData>
